--- a/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/mrt_cp_table.xlsx
@@ -460,19 +460,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1258271604938271</v>
+        <v>0.1282273860398861</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9142857142857144</v>
+        <v>1.088235294117647</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02564364193873573</v>
+        <v>0.02666955001712832</v>
       </c>
     </row>
     <row r="3">
@@ -480,19 +480,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06134920634920635</v>
+        <v>0.05827362996480642</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9928571428571429</v>
+        <v>1.21764705882353</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03868589716493313</v>
+        <v>0.04300335725384571</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02777777777777777</v>
+        <v>0.03676470588235292</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9535714285714286</v>
+        <v>1.311764705882353</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03106663893023783</v>
+        <v>0.04209982461487036</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +520,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01481481481481482</v>
+        <v>0.02638888888888891</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9535714285714286</v>
+        <v>1.28235294117647</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04021272798584414</v>
+        <v>0.05319474496568836</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="E6" t="n">
-        <v>0.95</v>
+        <v>1.252941176470588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03883215816738117</v>
+        <v>0.0447557341588758</v>
       </c>
     </row>
     <row r="7">
@@ -563,16 +563,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="E7" t="n">
-        <v>0.95</v>
+        <v>1.288235294117647</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03883215816738117</v>
+        <v>0.04917622040778217</v>
       </c>
     </row>
   </sheetData>
